--- a/public/files/Data_By_Towns_Index/Camden/Berlin Borough.xlsx
+++ b/public/files/Data_By_Towns_Index/Camden/Berlin Borough.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,385 +425,961 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DESAI RONAK M &amp; DEEP</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>32 SMOKEY RUN DRIVE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>-74.9262502</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.7850067</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJSztgeQstwYkRIaZWaxZ5F9Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATEL, TARLIKA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7 HARMONY LANE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-74.9263225</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39.78354390000001</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJBTyfjAstwYkRUgZNY2LEAwI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SHAH KUSHAL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20 GLACIER DRIVE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>-74.94257039999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39.7877812</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJtyWBExUtwYkRnOU0Z3pk56s</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GANDHI MELISSA &amp; KRUNAL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>85 GLACIER DRIVE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-74.9433681</v>
+      </c>
+      <c r="G5" t="n">
+        <v>39.7882628</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJ6VyPQhUtwYkRNgiTBWGa5LQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SHAH PANKAJ J &amp; KETKI P</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>41 BRYCE ROAD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>-74.9452728</v>
+      </c>
+      <c r="G6" t="n">
+        <v>39.7883906</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJc3w9wj8twYkRVA7K7aOp7NI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SHAH, BHARTI R</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>25 ZION DRIVE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-74.9464732</v>
+      </c>
+      <c r="G7" t="n">
+        <v>39.7891173</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ChIJA2OBmj8twYkRk1ZpBkTHv_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TRIVEDI VEDANT &amp; PANDYA JALPA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>107 SEQUOIA DRIVE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>-74.9478637</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39.7879814</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ChIJm93FBD8twYkRFvJSTzqxEoU</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PATEL ASHWINKUMAR M &amp; RASHMIBEN A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>104 WYNDAM ROAD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>-74.950273</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.788317</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ChIJ3d0G0zgtwYkRFPBV2cL1Yvs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PATEL PRITI J &amp; JAYPRAKASH N</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>215 ROOSEVELT BLVD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>-74.95094999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39.7899439</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ChIJdVoXpTgtwYkRqN7MQZ3OKCw</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PATEL DHARANI &amp; TARLIKA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>114 LINCOLN LANE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>-74.95164579999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39.7911277</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ChIJI_2UZ0ctwYkRKsTC36Eba8g</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PATEL, BHAVANA N</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>103 STOCKTON BLVD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>-74.95321229999999</v>
+      </c>
+      <c r="G12" t="n">
+        <v>39.791923</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ChIJu7Son0ctwYkRzAQi7zKTTZQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PANDYA, JITENDRA T &amp; MALVIKA J</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>105 STOCKTON BLVD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>-74.95341379999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39.7920807</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ChIJffYBokctwYkRbyUSpHo-QpU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SHAH VIKRAM &amp; ISHWARI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>211 STOCKTON BLVD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>-74.954576</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.7943085</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ChIJO-GPOEYtwYkRPnmW0YB3NV4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>DESAI, SHARAD &amp; DIPTI</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>209 RUTGERS BLVD</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Desai</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-74.9535633</v>
+      </c>
+      <c r="G15" t="n">
         <v>39.7954692</v>
       </c>
-      <c r="G2" t="n">
-        <v>-74.9535633</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>GUPTA, RAKESH</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>40 TANSBORO ROAD 707C</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Gupta</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>39.7885335</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-74.92800199999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GUPTA, RAKESH</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>40 TANSBORO ROAD 707D</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Gupta</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>39.7885335</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-74.92800199999999</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PATEL, BHAVANA N</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>103 STOCKTON BLVD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>39.791923</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-74.95321229999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PATEL, BHUPEN P &amp; JAYSHREE B</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>255 WHITE HORSE PIKE WEST</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>39.7727285</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-74.9029774</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ChIJD1nIe0YtwYkRBPfH5WboqBg</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JOSHI DEEPAK M &amp; GAYATRI D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>202 RUTGERS BLVD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>-74.95284049999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>39.7947884</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ChIJG9zUi0YtwYkRzg8q4TMX6_o</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RAVAL, NARENDRA G &amp; BINA N</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>308 STOCKTON BLVD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>-74.9541763</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39.79675</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ChIJ7V-Dw0UtwYkRBC__JkNyoGs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>PATEL, JIGNESH N &amp; AMITA</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>309 RUTGERS BLVD</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>-74.953766</v>
+      </c>
+      <c r="G18" t="n">
         <v>39.7971074</v>
       </c>
-      <c r="G7" t="n">
-        <v>-74.953766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ChIJPYsIyEUtwYkRu5X0geyHKuc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZAVERI, HITENDRA &amp; MEENA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>309 STOCKTON BLVD</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>-74.95492059999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>39.796961</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ChIJ0was7kUtwYkR2bmOY4sz2Wo</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PATEL KALPANA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>128 ELLIS AVENUE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>-74.95823850000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>39.8001463</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ChIJVTGSt08twYkRb8di1jAcdRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PATEL DARSHNA J</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4 OVERLOOK COURT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>-74.9623735</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39.8003605</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ChIJwxeq200twYkR-hnjnLrWqI0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SHAH CHHAYA R</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>84 EGG HARBOR ROAD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>-74.9489911</v>
+      </c>
+      <c r="G22" t="n">
+        <v>39.8061082</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ChIJS56AvF4twYkRTi3T5g43kB0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PATEL SANJAY &amp; RINKAL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23 CANYON DRIVE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>-74.94614109999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>39.790979</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ChIJ-7WaaUAtwYkRc603QDmDSHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>PATEL, PIYUSH &amp; JAIMESH</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>9 HILLSIDE LANE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>-74.9272316</v>
+      </c>
+      <c r="G24" t="n">
         <v>39.8005915</v>
       </c>
-      <c r="G8" t="n">
-        <v>-74.9272316</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PATEL, TARLIKA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>7 HARMONY LANE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Patel</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>39.78354390000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-74.9263225</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SHAH, BHARTI R</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>25 ZION DRIVE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Shah</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>39.7891173</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-74.9464732</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PANDYA, JITENDRA T &amp; MALVIKA J</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>105 STOCKTON BLVD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Pandya</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>39.7920807</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-74.95341379999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RAVAL, NARENDRA G &amp; BINA N</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>308 STOCKTON BLVD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Berlin Borough</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Raval</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>39.79675</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-74.9541763</v>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ChIJf95r2nstwYkRQx08XYWKxlU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PATEL SAPAN &amp; HETALBEN &amp; SAMIP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20 HILLSIDE LANE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Berlin Borough</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Camden</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>-74.9263467</v>
+      </c>
+      <c r="G25" t="n">
+        <v>39.7999453</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ChIJ4WrSeHktwYkRbF2vCkqJOnk</t>
+        </is>
       </c>
     </row>
   </sheetData>
